--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5629D010-CEA3-4949-87B2-E0032AEB52CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDF368E-C062-7B48-9025-7256C8C51ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="17260" yWindow="2640" windowWidth="20280" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>ETTh2</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>Baselines</t>
+  </si>
+  <si>
+    <t>VerbalTS-Backbone</t>
+  </si>
+  <si>
+    <t>Posterior Sample</t>
   </si>
 </sst>
 </file>
@@ -443,18 +449,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA88CAE-8538-1C4B-BF78-B0AFB8480CBE}">
-  <dimension ref="E8:I16"/>
+  <dimension ref="E8:J16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="5:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="5:10" x14ac:dyDescent="0.2">
       <c r="G8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="5:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="5:10" x14ac:dyDescent="0.2">
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="5:10" x14ac:dyDescent="0.2">
       <c r="G10" t="s">
         <v>4</v>
       </c>
@@ -464,8 +476,11 @@
       <c r="I10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="5:9" x14ac:dyDescent="0.2">
+      <c r="J10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="5:10" x14ac:dyDescent="0.2">
       <c r="E11" t="s">
         <v>3</v>
       </c>
@@ -481,8 +496,11 @@
       <c r="I11">
         <v>1.804</v>
       </c>
-    </row>
-    <row r="12" spans="5:9" x14ac:dyDescent="0.2">
+      <c r="J11">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="5:10" x14ac:dyDescent="0.2">
       <c r="F12" t="s">
         <v>1</v>
       </c>
@@ -495,8 +513,11 @@
       <c r="I12">
         <v>0.248</v>
       </c>
-    </row>
-    <row r="13" spans="5:9" x14ac:dyDescent="0.2">
+      <c r="J12">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="13" spans="5:10" x14ac:dyDescent="0.2">
       <c r="F13" t="s">
         <v>2</v>
       </c>
@@ -509,8 +530,11 @@
       <c r="I13">
         <v>0.307</v>
       </c>
-    </row>
-    <row r="14" spans="5:9" x14ac:dyDescent="0.2">
+      <c r="J13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="5:10" x14ac:dyDescent="0.2">
       <c r="E14" t="s">
         <v>7</v>
       </c>
@@ -526,8 +550,11 @@
       <c r="I14">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="15" spans="5:9" x14ac:dyDescent="0.2">
+      <c r="J14">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="5:10" x14ac:dyDescent="0.2">
       <c r="F15" t="s">
         <v>1</v>
       </c>
@@ -540,8 +567,11 @@
       <c r="I15">
         <v>9.2999999999999999E-2</v>
       </c>
-    </row>
-    <row r="16" spans="5:9" x14ac:dyDescent="0.2">
+      <c r="J15">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="5:10" x14ac:dyDescent="0.2">
       <c r="F16" t="s">
         <v>2</v>
       </c>
@@ -553,6 +583,9 @@
       </c>
       <c r="I16">
         <v>0.11</v>
+      </c>
+      <c r="J16">
+        <v>1.6E-2</v>
       </c>
     </row>
   </sheetData>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDF368E-C062-7B48-9025-7256C8C51ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EDA682-969C-A846-9470-532FADB2F4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17260" yWindow="2640" windowWidth="20280" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EDA682-969C-A846-9470-532FADB2F4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F170E5-789B-2640-814A-ECABDFFA2EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17260" yWindow="2640" windowWidth="20280" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="6220" yWindow="2640" windowWidth="31320" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>ETTh2</t>
   </si>
@@ -69,13 +69,25 @@
   </si>
   <si>
     <t>Posterior Sample</t>
+  </si>
+  <si>
+    <t>Imagen-backbone</t>
+  </si>
+  <si>
+    <t>Prior Sample</t>
+  </si>
+  <si>
+    <t>I need to resume training</t>
+  </si>
+  <si>
+    <t>Mine</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -83,8 +95,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -93,7 +112,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -110,9 +147,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -449,146 +507,224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA88CAE-8538-1C4B-BF78-B0AFB8480CBE}">
-  <dimension ref="E8:J16"/>
+  <dimension ref="E7:M16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="G8" s="1" t="s">
+    <row r="7" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="J9" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="G10" t="s">
+      <c r="K9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="E11" t="s">
+      <c r="K10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="5">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>0.151</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="5">
         <v>1.804</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="6">
         <v>2.7E-2</v>
       </c>
-    </row>
-    <row r="12" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="F12" t="s">
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+    </row>
+    <row r="12" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="5">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>1.056</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="5">
         <v>0.248</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="6">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="13" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="F13" t="s">
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+    </row>
+    <row r="13" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="5">
         <v>0.249</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <v>0.26</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="5">
         <v>0.307</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="14" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="E14" t="s">
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="5">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="5">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="15" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="F15" t="s">
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="5">
         <v>1.4E-2</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>0.28899999999999998</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="5">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="6">
         <v>1.2E-2</v>
       </c>
-    </row>
-    <row r="16" spans="5:10" x14ac:dyDescent="0.2">
-      <c r="F16" t="s">
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="5">
         <v>3.9E-2</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="5">
         <v>0.11</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="6">
         <v>1.6E-2</v>
       </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:M7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F170E5-789B-2640-814A-ECABDFFA2EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD90CED-2F28-2349-8930-BCEF1A179FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6220" yWindow="2640" windowWidth="31320" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="17740" yWindow="2600" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>ETTh2</t>
   </si>
@@ -81,6 +81,42 @@
   </si>
   <si>
     <t>Mine</t>
+  </si>
+  <si>
+    <t>Neurip2025</t>
+  </si>
+  <si>
+    <t>Neurips2024</t>
+  </si>
+  <si>
+    <t>old</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>StarLightCurves</t>
+  </si>
+  <si>
+    <t>Sine</t>
+  </si>
+  <si>
+    <t>SelfRegulationSCP1</t>
+  </si>
+  <si>
+    <t>SaugeenRiverFlow</t>
+  </si>
+  <si>
+    <t>ILI</t>
+  </si>
+  <si>
+    <t>ETThm1</t>
+  </si>
+  <si>
+    <t>ETThm2</t>
+  </si>
+  <si>
+    <t>Avg</t>
   </si>
 </sst>
 </file>
@@ -118,12 +154,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -131,6 +161,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -147,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -155,24 +191,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,11 +547,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA88CAE-8538-1C4B-BF78-B0AFB8480CBE}">
-  <dimension ref="E7:M16"/>
+  <dimension ref="E7:M34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" customWidth="1"/>
     <col min="11" max="11" width="17.6640625" customWidth="1"/>
     <col min="12" max="12" width="15.5" customWidth="1"/>
     <col min="13" max="13" width="15.6640625" customWidth="1"/>
@@ -520,11 +561,11 @@
     <row r="7" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
       <c r="J7" s="2" t="s">
         <v>14</v>
       </c>
@@ -535,57 +576,63 @@
     <row r="8" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="4" t="s">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
     </row>
     <row r="9" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="8" t="s">
+      <c r="G9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -596,128 +643,386 @@
       <c r="F11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="8">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="8">
         <v>0.151</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="8">
         <v>1.804</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="4">
         <v>2.7E-2</v>
       </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
     </row>
     <row r="12" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="8">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="8">
         <v>1.056</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="8">
         <v>0.248</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
         <v>0.02</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
     </row>
     <row r="13" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="8">
         <v>0.249</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="8">
         <v>0.26</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="8">
         <v>0.307</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
     </row>
     <row r="14" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1.4590000000000001</v>
+      </c>
+      <c r="H14" s="8">
+        <v>2.2467999999999999</v>
+      </c>
+      <c r="I14" s="8">
+        <v>5.2359999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="H15" s="8">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="I15" s="8">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="8">
+        <v>3.15E-3</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1.1900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="8">
+        <v>2.17</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1.4490000000000001</v>
+      </c>
+      <c r="I17" s="8">
+        <v>1.861</v>
+      </c>
+    </row>
+    <row r="18" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="8">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="H18" s="8">
+        <v>4.6699999999999997E-3</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="19" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="8">
+        <v>1.5329999999999999</v>
+      </c>
+      <c r="H19" s="8">
+        <v>1.921</v>
+      </c>
+      <c r="I19" s="8">
+        <v>1.718</v>
+      </c>
+    </row>
+    <row r="20" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="8">
+        <v>8.3199999999999993E-3</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1.49E-2</v>
+      </c>
+      <c r="I20" s="8">
+        <v>1.9890000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="8">
+        <v>2.4E-2</v>
+      </c>
+      <c r="H21" s="8">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I21" s="8">
+        <v>1.6319999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="10">
+        <f>AVERAGE(G11:G21)</f>
+        <v>0.50531545454545457</v>
+      </c>
+      <c r="H22" s="10">
+        <f t="shared" ref="H22:I22" si="0">AVERAGE(H11:H21)</f>
+        <v>0.65110636363636365</v>
+      </c>
+      <c r="I22" s="10">
+        <f t="shared" si="0"/>
+        <v>1.4459909090909091</v>
+      </c>
+    </row>
+    <row r="23" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G23" s="8">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H23" s="8">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I23" s="8">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J23" s="4">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-    </row>
-    <row r="15" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="E15" s="1"/>
-      <c r="F15" s="1" t="s">
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G24" s="8">
         <v>1.4E-2</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H24" s="8">
         <v>0.28899999999999998</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I24" s="8">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J24" s="4">
         <v>1.2E-2</v>
       </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+    </row>
+    <row r="25" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E25" s="1"/>
+      <c r="F25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G25" s="8">
         <v>3.9E-2</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H25" s="8">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I25" s="8">
         <v>0.11</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J25" s="4">
         <v>1.6E-2</v>
       </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+    </row>
+    <row r="26" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0.1986</v>
+      </c>
+      <c r="H26" s="8">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="I26" s="8">
+        <v>0.4138</v>
+      </c>
+    </row>
+    <row r="27" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="8">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="H27" s="8">
+        <v>1.37E-2</v>
+      </c>
+      <c r="I27" s="8">
+        <v>3.1699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="8">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="H28" s="8">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="I28" s="8">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0.16389999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="8">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="H30" s="10">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="I30" s="8">
+        <v>0.1067</v>
+      </c>
+    </row>
+    <row r="31" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0.38629999999999998</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0.42380000000000001</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0.379</v>
+      </c>
+    </row>
+    <row r="32" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="F32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="8">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="H32" s="8">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0.31459999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="8">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="H33" s="8">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0.22670000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="10">
+        <f>AVERAGE(G24:G33,G23)</f>
+        <v>0.10349090909090909</v>
+      </c>
+      <c r="H34" s="10">
+        <f t="shared" ref="H34:I34" si="1">AVERAGE(H24:H33,H23)</f>
+        <v>0.10581818181818181</v>
+      </c>
+      <c r="I34" s="10">
+        <f t="shared" si="1"/>
+        <v>0.19494545454545456</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD90CED-2F28-2349-8930-BCEF1A179FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4BE8B1-7414-B240-B3D5-E22CE89FF7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17740" yWindow="2600" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
@@ -89,9 +89,6 @@
     <t>Neurips2024</t>
   </si>
   <si>
-    <t>old</t>
-  </si>
-  <si>
     <t>Weather</t>
   </si>
   <si>
@@ -117,6 +114,9 @@
   </si>
   <si>
     <t>Avg</t>
+  </si>
+  <si>
+    <t>ICLR Old</t>
   </si>
 </sst>
 </file>
@@ -596,7 +596,7 @@
         <v>16</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>10</v>
@@ -703,7 +703,7 @@
     </row>
     <row r="14" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G14" s="8">
         <v>1.4590000000000001</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="15" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="8">
         <v>1.0500000000000001E-2</v>
@@ -731,7 +731,7 @@
     </row>
     <row r="16" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" s="8">
         <v>3.15E-3</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="17" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" s="8">
         <v>2.17</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="18" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G18" s="8">
         <v>8.5000000000000006E-3</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="19" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" s="8">
         <v>1.5329999999999999</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="20" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" s="8">
         <v>8.3199999999999993E-3</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="21" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G21" s="8">
         <v>2.4E-2</v>
@@ -815,7 +815,7 @@
     </row>
     <row r="22" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F22" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G22" s="10">
         <f>AVERAGE(G11:G21)</f>
@@ -897,7 +897,7 @@
     </row>
     <row r="26" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G26" s="8">
         <v>0.1986</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="27" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F27" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" s="8">
         <v>1.0699999999999999E-2</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="28" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G28" s="8">
         <v>9.5999999999999992E-3</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="29" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G29" s="8">
         <v>0.45500000000000002</v>
@@ -953,7 +953,7 @@
     </row>
     <row r="30" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F30" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G30" s="8">
         <v>5.1000000000000004E-3</v>
@@ -967,7 +967,7 @@
     </row>
     <row r="31" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F31" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G31" s="8">
         <v>0.38629999999999998</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="32" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F32" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G32" s="8">
         <v>3.0999999999999999E-3</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="33" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F33" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G33" s="8">
         <v>6.0000000000000001E-3</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="34" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F34" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G34" s="10">
         <f>AVERAGE(G24:G33,G23)</f>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4BE8B1-7414-B240-B3D5-E22CE89FF7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED5E516-2B0C-8E44-8A9C-23A1E4E0889A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17740" yWindow="2600" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="6980" yWindow="2600" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -188,16 +188,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -209,10 +203,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,73 +566,73 @@
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="3" t="s">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
     </row>
     <row r="9" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -643,75 +643,81 @@
       <c r="F11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="6">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="6">
         <v>0.151</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="6">
         <v>1.804</v>
       </c>
-      <c r="J11" s="4">
-        <v>2.7E-2</v>
-      </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+      <c r="J11" s="3">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
     </row>
     <row r="12" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="6">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="6">
         <v>1.056</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="6">
         <v>0.248</v>
       </c>
-      <c r="J12" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+      <c r="J12" s="3">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="K12" s="2">
+        <v>3.85</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
     </row>
     <row r="13" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="6">
         <v>0.249</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="6">
         <v>0.26</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="6">
         <v>0.307</v>
       </c>
-      <c r="J13" s="4">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="J13" s="3">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="K13" s="2">
+        <v>3.39</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="6">
         <v>1.4590000000000001</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="6">
         <v>2.2467999999999999</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="6">
         <v>5.2359999999999998</v>
       </c>
     </row>
@@ -719,13 +725,13 @@
       <c r="F15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="6">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="6">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="6">
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
@@ -733,13 +739,13 @@
       <c r="F16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="6">
         <v>3.15E-3</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="6">
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="6">
         <v>1.1900000000000001E-2</v>
       </c>
     </row>
@@ -747,13 +753,13 @@
       <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="6">
         <v>2.17</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="6">
         <v>1.4490000000000001</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="6">
         <v>1.861</v>
       </c>
     </row>
@@ -761,13 +767,13 @@
       <c r="F18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="6">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="6">
         <v>4.6699999999999997E-3</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="6">
         <v>1.02</v>
       </c>
     </row>
@@ -775,13 +781,13 @@
       <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="6">
         <v>1.5329999999999999</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="6">
         <v>1.921</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="6">
         <v>1.718</v>
       </c>
     </row>
@@ -789,13 +795,13 @@
       <c r="F20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="6">
         <v>8.3199999999999993E-3</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="6">
         <v>1.49E-2</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="6">
         <v>1.9890000000000001</v>
       </c>
     </row>
@@ -803,29 +809,29 @@
       <c r="F21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="6">
         <v>3.3700000000000001E-2</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="6">
         <v>1.6319999999999999</v>
       </c>
     </row>
     <row r="22" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="7">
         <f>AVERAGE(G11:G21)</f>
         <v>0.50531545454545457</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="7">
         <f t="shared" ref="H22:I22" si="0">AVERAGE(H11:H21)</f>
         <v>0.65110636363636365</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="7">
         <f t="shared" si="0"/>
         <v>1.4459909090909091</v>
       </c>
@@ -837,75 +843,81 @@
       <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="6">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="6">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="6">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J23" s="4">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="J23" s="3">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="K23" s="2">
+        <v>0.35160000000000002</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
     </row>
     <row r="24" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="6">
         <v>0.28899999999999998</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="6">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J24" s="4">
-        <v>1.2E-2</v>
-      </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
+      <c r="J24" s="3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
     </row>
     <row r="25" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="6">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="6">
         <v>0.11</v>
       </c>
-      <c r="J25" s="4">
-        <v>1.6E-2</v>
-      </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
+      <c r="J25" s="3">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
     </row>
     <row r="26" spans="5:13" x14ac:dyDescent="0.2">
       <c r="F26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="6">
         <v>0.1986</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="6">
         <v>1.9300000000000001E-2</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="6">
         <v>0.4138</v>
       </c>
     </row>
@@ -913,13 +925,13 @@
       <c r="F27" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="6">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="6">
         <v>1.37E-2</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="6">
         <v>3.1699999999999999E-2</v>
       </c>
     </row>
@@ -927,13 +939,13 @@
       <c r="F28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="6">
         <v>9.5999999999999992E-3</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="6">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -941,13 +953,13 @@
       <c r="F29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="6">
         <v>0.45500000000000002</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="7">
         <v>0.28299999999999997</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="6">
         <v>0.16389999999999999</v>
       </c>
     </row>
@@ -955,13 +967,13 @@
       <c r="F30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="6">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="7">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="6">
         <v>0.1067</v>
       </c>
     </row>
@@ -969,13 +981,13 @@
       <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="6">
         <v>0.38629999999999998</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="7">
         <v>0.42380000000000001</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="6">
         <v>0.379</v>
       </c>
     </row>
@@ -983,13 +995,13 @@
       <c r="F32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="6">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="6">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="6">
         <v>0.31459999999999999</v>
       </c>
     </row>
@@ -997,13 +1009,13 @@
       <c r="F33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="6">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="6">
         <v>0.22670000000000001</v>
       </c>
     </row>
@@ -1011,15 +1023,15 @@
       <c r="F34" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="7">
         <f>AVERAGE(G24:G33,G23)</f>
         <v>0.10349090909090909</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="7">
         <f t="shared" ref="H34:I34" si="1">AVERAGE(H24:H33,H23)</f>
         <v>0.10581818181818181</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="7">
         <f t="shared" si="1"/>
         <v>0.19494545454545456</v>
       </c>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED5E516-2B0C-8E44-8A9C-23A1E4E0889A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8074081-D367-114D-A268-58D031CD1D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6980" yWindow="2600" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="3140" yWindow="2980" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8074081-D367-114D-A268-58D031CD1D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D94E27-F0C0-EF44-877C-65955383A0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3140" yWindow="2980" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="9040" yWindow="3020" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -656,10 +656,14 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="K11" s="2">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="M11" s="2">
+        <v>5.6000000000000001E-2</v>
+      </c>
     </row>
     <row r="12" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E12" s="1"/>
@@ -678,10 +682,10 @@
       <c r="J12" s="3">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="K12" s="2">
-        <v>3.85</v>
-      </c>
-      <c r="L12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2">
+        <v>0.01</v>
+      </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="5:13" x14ac:dyDescent="0.2">
@@ -701,10 +705,10 @@
       <c r="J13" s="3">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="K13" s="2">
-        <v>3.39</v>
-      </c>
-      <c r="L13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2">
+        <v>4.8000000000000001E-2</v>
+      </c>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="5:13" x14ac:dyDescent="0.2">
@@ -853,13 +857,17 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J23" s="3">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="K23" s="2">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L23" s="2">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="K23" s="2">
-        <v>0.35160000000000002</v>
-      </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
+      <c r="M23" s="2">
+        <v>4.7E-2</v>
+      </c>
     </row>
     <row r="24" spans="5:13" x14ac:dyDescent="0.2">
       <c r="E24" s="1"/>
@@ -878,10 +886,10 @@
       <c r="J24" s="3">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="K24" s="2">
-        <v>0.42</v>
-      </c>
-      <c r="L24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2">
+        <v>1.2999999999999999E-2</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="5:13" x14ac:dyDescent="0.2">
@@ -901,10 +909,10 @@
       <c r="J25" s="3">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="K25" s="2">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="L25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2">
+        <v>5.7999999999999996E-3</v>
+      </c>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="5:13" x14ac:dyDescent="0.2">

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D94E27-F0C0-EF44-877C-65955383A0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169D263F-32BC-AE4A-B3D7-4DD79D2BCA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9040" yWindow="3020" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="3140" yWindow="3020" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169D263F-32BC-AE4A-B3D7-4DD79D2BCA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C811F027-15A8-D843-9B0C-7B9C1FF8946A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3140" yWindow="3020" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="8740" yWindow="3780" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>ETTh2</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>ICLR Old</t>
+  </si>
+  <si>
+    <t>Prior Sample V2</t>
   </si>
 </sst>
 </file>
@@ -547,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA88CAE-8538-1C4B-BF78-B0AFB8480CBE}">
-  <dimension ref="E7:M34"/>
+  <dimension ref="E7:N34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
@@ -556,9 +559,10 @@
     <col min="11" max="11" width="17.6640625" customWidth="1"/>
     <col min="12" max="12" width="15.5" customWidth="1"/>
     <col min="13" max="13" width="15.6640625" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="9" t="s">
@@ -573,7 +577,7 @@
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
     </row>
-    <row r="8" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="6"/>
@@ -586,7 +590,7 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="6" t="s">
@@ -610,8 +614,11 @@
       <c r="M9" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="6" t="s">
@@ -635,8 +642,11 @@
       <c r="M10" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
@@ -664,8 +674,11 @@
       <c r="M11" s="2">
         <v>5.6000000000000001E-2</v>
       </c>
-    </row>
-    <row r="12" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="2">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
         <v>1</v>
@@ -687,8 +700,11 @@
         <v>0.01</v>
       </c>
       <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="2">
+        <v>7.8299999999999995E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
         <v>2</v>
@@ -710,8 +726,11 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="2">
+        <v>0.40899999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
         <v>17</v>
       </c>
@@ -725,7 +744,7 @@
         <v>5.2359999999999998</v>
       </c>
     </row>
-    <row r="15" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F15" s="1" t="s">
         <v>18</v>
       </c>
@@ -739,7 +758,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F16" s="1" t="s">
         <v>19</v>
       </c>
@@ -753,7 +772,7 @@
         <v>1.1900000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
@@ -767,7 +786,7 @@
         <v>1.861</v>
       </c>
     </row>
-    <row r="18" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F18" s="1" t="s">
         <v>21</v>
       </c>
@@ -781,7 +800,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="19" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
@@ -795,7 +814,7 @@
         <v>1.718</v>
       </c>
     </row>
-    <row r="20" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F20" s="1" t="s">
         <v>23</v>
       </c>
@@ -809,7 +828,7 @@
         <v>1.9890000000000001</v>
       </c>
     </row>
-    <row r="21" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F21" s="1" t="s">
         <v>24</v>
       </c>
@@ -823,7 +842,7 @@
         <v>1.6319999999999999</v>
       </c>
     </row>
-    <row r="22" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F22" s="5" t="s">
         <v>25</v>
       </c>
@@ -840,7 +859,7 @@
         <v>1.4459909090909091</v>
       </c>
     </row>
-    <row r="23" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
@@ -868,8 +887,11 @@
       <c r="M23" s="2">
         <v>4.7E-2</v>
       </c>
-    </row>
-    <row r="24" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="2">
+        <v>1.5800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
         <v>1</v>
@@ -891,8 +913,11 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="M24" s="2"/>
-    </row>
-    <row r="25" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="2">
+        <v>5.8599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
         <v>2</v>
@@ -914,8 +939,11 @@
         <v>5.7999999999999996E-3</v>
       </c>
       <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="2">
+        <v>0.13750000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F26" s="1" t="s">
         <v>17</v>
       </c>
@@ -929,7 +957,7 @@
         <v>0.4138</v>
       </c>
     </row>
-    <row r="27" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F27" s="1" t="s">
         <v>18</v>
       </c>
@@ -943,7 +971,7 @@
         <v>3.1699999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F28" s="1" t="s">
         <v>19</v>
       </c>
@@ -957,7 +985,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F29" s="1" t="s">
         <v>20</v>
       </c>
@@ -971,7 +999,7 @@
         <v>0.16389999999999999</v>
       </c>
     </row>
-    <row r="30" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F30" s="1" t="s">
         <v>21</v>
       </c>
@@ -985,7 +1013,7 @@
         <v>0.1067</v>
       </c>
     </row>
-    <row r="31" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
@@ -999,7 +1027,7 @@
         <v>0.379</v>
       </c>
     </row>
-    <row r="32" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F32" s="1" t="s">
         <v>23</v>
       </c>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C811F027-15A8-D843-9B0C-7B9C1FF8946A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FAFE2C-BC01-E146-9AB5-2B400A9EB564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8740" yWindow="3780" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="1180" yWindow="4980" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>ETTh2</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>Prior Sample</t>
-  </si>
-  <si>
-    <t>I need to resume training</t>
   </si>
   <si>
     <t>Mine</t>
@@ -142,7 +139,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,25 +148,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -186,36 +177,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA88CAE-8538-1C4B-BF78-B0AFB8480CBE}">
-  <dimension ref="E7:N34"/>
+  <dimension ref="E7:X34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
@@ -562,299 +552,305 @@
     <col min="14" max="14" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-    </row>
-    <row r="8" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="7"/>
+    </row>
+    <row r="9" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="5:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="5:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.151</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1.804</v>
+      </c>
+      <c r="J11" s="9">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="K11" s="8">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="M11" s="8">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="H11" s="6">
-        <v>0.151</v>
-      </c>
-      <c r="I11" s="6">
-        <v>1.804</v>
-      </c>
-      <c r="J11" s="3">
-        <v>2.4899999999999999E-2</v>
-      </c>
-      <c r="K11" s="2">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="L11" s="2">
+      <c r="N11" s="8">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="5:24" x14ac:dyDescent="0.2">
+      <c r="E12" s="1"/>
+      <c r="F12" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1.056</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.248</v>
+      </c>
+      <c r="J12" s="9">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8">
         <v>0.01</v>
       </c>
-      <c r="M11" s="2">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="N11" s="2">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="6">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="H12" s="6">
-        <v>1.056</v>
-      </c>
-      <c r="I12" s="6">
-        <v>0.248</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2">
+      <c r="M12" s="8"/>
+      <c r="N12" s="8">
         <v>7.8299999999999995E-2</v>
       </c>
     </row>
-    <row r="13" spans="5:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="6">
-        <v>0.249</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="G13" s="3">
         <v>0.26</v>
       </c>
-      <c r="I13" s="6">
+      <c r="H13" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="I13" s="3">
         <v>0.307</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="9">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2">
+      <c r="K13" s="8"/>
+      <c r="L13" s="8">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2">
+      <c r="M13" s="8"/>
+      <c r="N13" s="8">
         <v>0.40899999999999997</v>
       </c>
     </row>
-    <row r="14" spans="5:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="5:24" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1.4590000000000001</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2.2467999999999999</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5.2359999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="5:24" x14ac:dyDescent="0.2">
+      <c r="F15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="6">
-        <v>1.4590000000000001</v>
-      </c>
-      <c r="H14" s="6">
-        <v>2.2467999999999999</v>
-      </c>
-      <c r="I14" s="6">
-        <v>5.2359999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="3">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="H15" s="3">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="I15" s="3">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="5:24" x14ac:dyDescent="0.2">
+      <c r="F16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="6">
-        <v>1.0500000000000001E-2</v>
-      </c>
-      <c r="H15" s="6">
-        <v>8.2000000000000007E-3</v>
-      </c>
-      <c r="I15" s="6">
-        <v>7.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="F16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="G16" s="3">
         <v>3.15E-3</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="3">
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="3">
         <v>1.1900000000000001E-2</v>
       </c>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
     </row>
     <row r="17" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="6">
+        <v>19</v>
+      </c>
+      <c r="G17" s="3">
         <v>2.17</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="3">
         <v>1.4490000000000001</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="3">
         <v>1.861</v>
       </c>
     </row>
     <row r="18" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="6">
+        <v>20</v>
+      </c>
+      <c r="G18" s="3">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="3">
         <v>4.6699999999999997E-3</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="3">
         <v>1.02</v>
       </c>
     </row>
     <row r="19" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="6">
+        <v>21</v>
+      </c>
+      <c r="G19" s="3">
         <v>1.5329999999999999</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="3">
         <v>1.921</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="3">
         <v>1.718</v>
       </c>
     </row>
     <row r="20" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="6">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3">
         <v>8.3199999999999993E-3</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="3">
         <v>1.49E-2</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="3">
         <v>1.9890000000000001</v>
       </c>
     </row>
     <row r="21" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="H21" s="3">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1.6319999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="F22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="6">
-        <v>2.4E-2</v>
-      </c>
-      <c r="H21" s="6">
-        <v>3.3700000000000001E-2</v>
-      </c>
-      <c r="I21" s="6">
-        <v>1.6319999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="F22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="7">
+      <c r="G22" s="4">
         <f>AVERAGE(G11:G21)</f>
-        <v>0.50531545454545457</v>
-      </c>
-      <c r="H22" s="7">
+        <v>0.50229727272727276</v>
+      </c>
+      <c r="H22" s="4">
         <f t="shared" ref="H22:I22" si="0">AVERAGE(H11:H21)</f>
         <v>0.65110636363636365</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="4">
         <f t="shared" si="0"/>
         <v>1.4459909090909091</v>
       </c>
@@ -863,211 +859,211 @@
       <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="8">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="8">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="8">
         <v>4.7E-2</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="8">
         <v>1.5800000000000002E-2</v>
       </c>
     </row>
     <row r="24" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="3">
         <v>1.4E-2</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="3">
         <v>0.28899999999999998</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="3">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="9">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2">
+      <c r="K24" s="8"/>
+      <c r="L24" s="8">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2">
+      <c r="M24" s="8"/>
+      <c r="N24" s="8">
         <v>5.8599999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G25" s="6">
-        <v>3.9E-2</v>
-      </c>
-      <c r="H25" s="6">
+      <c r="G25" s="3">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="H25" s="3">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="3">
         <v>0.11</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25" s="9">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2">
+      <c r="K25" s="8"/>
+      <c r="L25" s="8">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2">
+      <c r="M25" s="8"/>
+      <c r="N25" s="8">
         <v>0.13750000000000001</v>
       </c>
     </row>
     <row r="26" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="6">
+        <v>16</v>
+      </c>
+      <c r="G26" s="3">
         <v>0.1986</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="3">
         <v>1.9300000000000001E-2</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="3">
         <v>0.4138</v>
       </c>
     </row>
     <row r="27" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="6">
+        <v>17</v>
+      </c>
+      <c r="G27" s="3">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="3">
         <v>1.37E-2</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="3">
         <v>3.1699999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="6">
+        <v>18</v>
+      </c>
+      <c r="G28" s="3">
         <v>9.5999999999999992E-3</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="3">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="29" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="6">
+        <v>19</v>
+      </c>
+      <c r="G29" s="3">
         <v>0.45500000000000002</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="4">
         <v>0.28299999999999997</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="3">
         <v>0.16389999999999999</v>
       </c>
     </row>
     <row r="30" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="6">
+        <v>20</v>
+      </c>
+      <c r="G30" s="3">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="4">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="3">
         <v>0.1067</v>
       </c>
     </row>
     <row r="31" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" s="6">
+        <v>21</v>
+      </c>
+      <c r="G31" s="3">
         <v>0.38629999999999998</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="4">
         <v>0.42380000000000001</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I31" s="3">
         <v>0.379</v>
       </c>
     </row>
     <row r="32" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="6">
+        <v>22</v>
+      </c>
+      <c r="G32" s="3">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="3">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="3">
         <v>0.31459999999999999</v>
       </c>
     </row>
     <row r="33" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="6">
+        <v>23</v>
+      </c>
+      <c r="G33" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="3">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="3">
         <v>0.22670000000000001</v>
       </c>
     </row>
     <row r="34" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="7">
+        <v>24</v>
+      </c>
+      <c r="G34" s="4">
         <f>AVERAGE(G24:G33,G23)</f>
-        <v>0.10349090909090909</v>
-      </c>
-      <c r="H34" s="7">
+        <v>0.10472727272727272</v>
+      </c>
+      <c r="H34" s="4">
         <f t="shared" ref="H34:I34" si="1">AVERAGE(H24:H33,H23)</f>
         <v>0.10581818181818181</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="4">
         <f t="shared" si="1"/>
         <v>0.19494545454545456</v>
       </c>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FAFE2C-BC01-E146-9AB5-2B400A9EB564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B600A03E-EB63-564E-AECA-DE611621A038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="4980" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="12320" yWindow="4780" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>ETTh2</t>
   </si>
@@ -117,6 +117,21 @@
   </si>
   <si>
     <t>Prior Sample V2</t>
+  </si>
+  <si>
+    <t>Synthetic-U</t>
+  </si>
+  <si>
+    <t>Synthetic-M</t>
+  </si>
+  <si>
+    <t>Text-conditional</t>
+  </si>
+  <si>
+    <t>Disc</t>
+  </si>
+  <si>
+    <t>ETTm1</t>
   </si>
 </sst>
 </file>
@@ -189,16 +204,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -206,6 +215,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA88CAE-8538-1C4B-BF78-B0AFB8480CBE}">
-  <dimension ref="E7:X34"/>
+  <dimension ref="E7:X61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
@@ -555,18 +570,18 @@
     <row r="7" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="6" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="7"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="6"/>
     </row>
     <row r="8" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E8" s="1"/>
@@ -574,11 +589,11 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="7"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="6"/>
     </row>
     <row r="9" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E9" s="1"/>
@@ -592,19 +607,19 @@
       <c r="I9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -620,19 +635,19 @@
       <c r="I10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -640,7 +655,7 @@
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="3">
@@ -652,25 +667,25 @@
       <c r="I11" s="3">
         <v>1.804</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="7">
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="5">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="5">
         <v>0.01</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="5">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="5">
         <v>5.5E-2</v>
       </c>
     </row>
     <row r="12" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E12" s="1"/>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>1</v>
       </c>
       <c r="G12" s="3">
@@ -682,21 +697,21 @@
       <c r="I12" s="3">
         <v>0.248</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="7">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8">
+      <c r="K12" s="5"/>
+      <c r="L12" s="5">
         <v>0.01</v>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8">
+      <c r="M12" s="5"/>
+      <c r="N12" s="5">
         <v>7.8299999999999995E-2</v>
       </c>
     </row>
     <row r="13" spans="5:24" x14ac:dyDescent="0.2">
       <c r="E13" s="1"/>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G13" s="3">
@@ -708,15 +723,15 @@
       <c r="I13" s="3">
         <v>0.307</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="7">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8">
+      <c r="K13" s="5"/>
+      <c r="L13" s="5">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8">
+      <c r="M13" s="5"/>
+      <c r="N13" s="5">
         <v>0.40899999999999997</v>
       </c>
     </row>
@@ -761,12 +776,12 @@
       <c r="I16" s="3">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
     </row>
     <row r="17" spans="5:14" x14ac:dyDescent="0.2">
       <c r="F17" s="1" t="s">
@@ -859,7 +874,7 @@
       <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G23" s="3">
@@ -871,25 +886,25 @@
       <c r="I23" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="7">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="5">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="5">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="5">
         <v>4.7E-2</v>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="5">
         <v>1.5800000000000002E-2</v>
       </c>
     </row>
     <row r="24" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E24" s="1"/>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="8" t="s">
         <v>1</v>
       </c>
       <c r="G24" s="3">
@@ -901,21 +916,21 @@
       <c r="I24" s="3">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="7">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8">
+      <c r="K24" s="5"/>
+      <c r="L24" s="5">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8">
+      <c r="M24" s="5"/>
+      <c r="N24" s="5">
         <v>5.8599999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E25" s="1"/>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G25" s="3">
@@ -927,15 +942,15 @@
       <c r="I25" s="3">
         <v>0.11</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="7">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8">
+      <c r="K25" s="5"/>
+      <c r="L25" s="5">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8">
+      <c r="M25" s="5"/>
+      <c r="N25" s="5">
         <v>0.13750000000000001</v>
       </c>
     </row>
@@ -1066,6 +1081,86 @@
       <c r="I34" s="4">
         <f t="shared" si="1"/>
         <v>0.19494545454545456</v>
+      </c>
+    </row>
+    <row r="53" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>5</v>
+      </c>
+      <c r="J53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="F54" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54">
+        <v>2.3E-3</v>
+      </c>
+      <c r="J54">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="G55" t="s">
+        <v>28</v>
+      </c>
+      <c r="H55">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="J55">
+        <v>3.7900000000000003E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="G56" t="s">
+        <v>31</v>
+      </c>
+      <c r="H56">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="J56">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="59" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="F59" t="s">
+        <v>30</v>
+      </c>
+      <c r="G59" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="J59">
+        <v>7.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="G60" t="s">
+        <v>28</v>
+      </c>
+      <c r="H60">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="J60">
+        <v>8.5000000000000006E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+      <c r="H61">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J61">
+        <v>5.0999999999999997E-2</v>
       </c>
     </row>
   </sheetData>

--- a/ExperimentData.xlsx
+++ b/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/ImagenFew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B600A03E-EB63-564E-AECA-DE611621A038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CC13A3-8D69-3F4B-AA24-3202B1A06273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12320" yWindow="4780" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
+    <workbookView xWindow="12240" yWindow="5260" windowWidth="31420" windowHeight="13060" xr2:uid="{E5419BAC-4B6F-E540-9397-DA349BE39778}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
   <si>
     <t>ETTh2</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>ETTm1</t>
+  </si>
+  <si>
+    <t>istanbul</t>
   </si>
 </sst>
 </file>
@@ -555,11 +558,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA88CAE-8538-1C4B-BF78-B0AFB8480CBE}">
-  <dimension ref="E7:X61"/>
+  <dimension ref="E7:X62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
     <col min="10" max="10" width="18.1640625" customWidth="1"/>
     <col min="11" max="11" width="17.6640625" customWidth="1"/>
     <col min="12" max="12" width="15.5" customWidth="1"/>
@@ -1099,10 +1103,10 @@
         <v>27</v>
       </c>
       <c r="H54">
-        <v>2.3E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="J54">
-        <v>1.9E-2</v>
+        <v>4.5999999999999999E-3</v>
       </c>
     </row>
     <row r="55" spans="6:10" x14ac:dyDescent="0.2">
@@ -1110,10 +1114,10 @@
         <v>28</v>
       </c>
       <c r="H55">
-        <v>1.0999999999999999E-2</v>
+        <v>1.78E-2</v>
       </c>
       <c r="J55">
-        <v>3.7900000000000003E-2</v>
+        <v>1.8800000000000001E-2</v>
       </c>
     </row>
     <row r="56" spans="6:10" x14ac:dyDescent="0.2">
@@ -1121,10 +1125,21 @@
         <v>31</v>
       </c>
       <c r="H56">
-        <v>1.2999999999999999E-2</v>
+        <v>1.26E-2</v>
       </c>
       <c r="J56">
-        <v>0.91</v>
+        <v>1.35E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="G57" t="s">
+        <v>32</v>
+      </c>
+      <c r="H57">
+        <v>1.78E-2</v>
+      </c>
+      <c r="J57">
+        <v>1.52E-2</v>
       </c>
     </row>
     <row r="59" spans="6:10" x14ac:dyDescent="0.2">
@@ -1135,10 +1150,10 @@
         <v>27</v>
       </c>
       <c r="H59">
-        <v>2.3999999999999998E-3</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="J59">
-        <v>7.4999999999999997E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
     </row>
     <row r="60" spans="6:10" x14ac:dyDescent="0.2">
@@ -1146,10 +1161,10 @@
         <v>28</v>
       </c>
       <c r="H60">
-        <v>2.7000000000000001E-3</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="J60">
-        <v>8.5000000000000006E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
     </row>
     <row r="61" spans="6:10" x14ac:dyDescent="0.2">
@@ -1157,10 +1172,21 @@
         <v>31</v>
       </c>
       <c r="H61">
-        <v>4.0000000000000001E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="J61">
-        <v>5.0999999999999997E-2</v>
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="G62" t="s">
+        <v>32</v>
+      </c>
+      <c r="H62">
+        <v>7.6E-3</v>
+      </c>
+      <c r="J62">
+        <v>5.7000000000000002E-3</v>
       </c>
     </row>
   </sheetData>
